--- a/DateBase/orders/Nha Thu_2026-3-25.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-25.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L57"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -865,10 +865,64 @@
       <c r="A51" t="str">
         <v>9</v>
       </c>
+      <c r="C51" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F52" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F53" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>107_绣球浅粉_Hydrangea Light Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F54" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>47_拉丝玫红_Spider Dark Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>605_康乃馨流光粉_light pink_undefined_20stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L57"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -923,7 +977,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0536612115152020151515105101055151515205151515105556512510331055404885652030200</v>
+        <v>05366121151520201515151051010551515152051515151055565125103310554048856520302010553015815</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-3-25.xlsx
+++ b/DateBase/orders/Nha Thu_2026-3-25.xlsx
@@ -979,6 +979,9 @@
       <c r="G2" t="str">
         <v>05366121151520201515151051010551515152051515151055565125103310554048856520302010553015815</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
